--- a/survey_templates/047_skin_pigmentation_assessment_quiz--survey_templates.xlsx
+++ b/survey_templates/047_skin_pigmentation_assessment_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mild'}</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mild'}</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_severe'}</t>
+          <t>very_severe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Severe'}</t>
+          <t>Very Severe</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hyper-pigmentation'}</t>
+          <t>hyper-pigmentation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Hyper-Pigmentation'}</t>
+          <t>Hyper-Pigmentation</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hypopigmentation'}</t>
+          <t>hypopigmentation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hypopigmentation'}</t>
+          <t>Hypopigmentation</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'skin_redness'}</t>
+          <t>skin_redness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Skin Redness'}</t>
+          <t>Skin Redness</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'skin_discoloration'}</t>
+          <t>skin_discoloration</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Skin Discoloration'}</t>
+          <t>Skin Discoloration</t>
         </is>
       </c>
     </row>
